--- a/events/Tokyo_2021_OG/Tokyo_2021_OG_Results.xlsx
+++ b/events/Tokyo_2021_OG/Tokyo_2021_OG_Results.xlsx
@@ -6782,6 +6782,11 @@
           <t>36313</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7067,6 +7072,11 @@
           <t>+1.663</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>45842</t>
@@ -11292,6 +11302,11 @@
           <t>36313</t>
         </is>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11357,6 +11372,11 @@
           <t>+0.128</t>
         </is>
       </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>45842</t>
@@ -15171,6 +15191,11 @@
           <t>36313</t>
         </is>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
       <c r="X209" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -15311,6 +15336,11 @@
           <t>+0.385</t>
         </is>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>45842</t>
@@ -19987,6 +20017,11 @@
           <t>+1.627</t>
         </is>
       </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S275" t="inlineStr">
         <is>
           <t>45842</t>
@@ -23028,6 +23063,11 @@
           <t>+0.876</t>
         </is>
       </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -24673,6 +24713,11 @@
           <t>1:49.402</t>
         </is>
       </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -25763,6 +25808,11 @@
           <t>+0.686</t>
         </is>
       </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -34997,6 +35047,11 @@
           <t>+1.678</t>
         </is>
       </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -36982,6 +37037,11 @@
           <t>+2.358</t>
         </is>
       </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -37047,6 +37107,11 @@
           <t>+2.555</t>
         </is>
       </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -39477,6 +39542,11 @@
           <t>+1.022</t>
         </is>
       </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -40393,6 +40463,11 @@
           <t>1:55.051</t>
         </is>
       </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -41453,6 +41528,11 @@
           <t>+3.118</t>
         </is>
       </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -43946,6 +44026,11 @@
           <t>+2.073</t>
         </is>
       </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S618" t="inlineStr">
         <is>
           <t>100406</t>
@@ -48821,6 +48906,11 @@
           <t>2:03.282</t>
         </is>
       </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S684" t="inlineStr">
         <is>
           <t>100406</t>
@@ -52040,6 +52130,11 @@
           <t>+2.286</t>
         </is>
       </c>
+      <c r="R728" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S728" t="inlineStr">
         <is>
           <t>100406</t>
@@ -56257,6 +56352,11 @@
       <c r="Q784" t="inlineStr">
         <is>
           <t>+6.128</t>
+        </is>
+      </c>
+      <c r="R784" t="inlineStr">
+        <is>
+          <t>95617</t>
         </is>
       </c>
       <c r="S784" t="inlineStr">
@@ -59217,7 +59317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64133,6 +64233,72 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>OSTERMAN</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Alyssa</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>BULL</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Yarisleidis</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>CIRILO DUBOYS</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Tokyo_2021_OG/Tokyo_2021_OG_Results.xlsx
+++ b/events/Tokyo_2021_OG/Tokyo_2021_OG_Results.xlsx
@@ -59350,7 +59350,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>da CONCEICAO TRISTE Buly</t>
+          <t>Buly</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>da CONCEICAO TRISTE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -59367,7 +59372,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>de JONGE Mark</t>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>de JONGE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -59384,7 +59394,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>van der WESTHUYZEN Jean</t>
+          <t>Jean</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>van der WESTHUYZEN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/events/Tokyo_2021_OG/Tokyo_2021_OG_Results.xlsx
+++ b/events/Tokyo_2021_OG/Tokyo_2021_OG_Results.xlsx
@@ -2267,6 +2267,11 @@
           <t>+1.157</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2602,6 +2607,11 @@
           <t>+0.825</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3542,6 +3552,11 @@
           <t>98917</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4187,6 +4202,11 @@
           <t>+5.546</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4737,6 +4757,11 @@
           <t>+11.496</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5142,6 +5167,11 @@
           <t>3:43.444</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6637,6 +6667,16 @@
           <t>+0.601</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8677,6 +8717,11 @@
           <t>+0.470</t>
         </is>
       </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9687,6 +9732,11 @@
           <t>3:44.136</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10237,6 +10287,11 @@
           <t>+0.864</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12717,6 +12772,11 @@
           <t>+0.720</t>
         </is>
       </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -13077,6 +13137,11 @@
           <t>98917</t>
         </is>
       </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14487,6 +14552,11 @@
           <t>+4.381</t>
         </is>
       </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14552,6 +14622,11 @@
           <t>+4.430</t>
         </is>
       </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -15411,6 +15486,16 @@
           <t>+0.474</t>
         </is>
       </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15920,6 +16005,11 @@
           <t>+0.415</t>
         </is>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -17986,6 +18076,11 @@
           <t>98917</t>
         </is>
       </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -18264,6 +18359,11 @@
           <t>+1.021</t>
         </is>
       </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -18331,6 +18431,11 @@
           <t>+1.740</t>
         </is>
       </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -20094,6 +20199,16 @@
           <t>+1.862</t>
         </is>
       </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -20448,6 +20563,11 @@
           <t>+0.459</t>
         </is>
       </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -23478,6 +23598,11 @@
           <t>+0.718</t>
         </is>
       </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -23543,6 +23668,11 @@
           <t>+1.323</t>
         </is>
       </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>63942</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -24853,6 +24983,11 @@
           <t>+1.330</t>
         </is>
       </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -25468,6 +25603,11 @@
           <t>+4.167</t>
         </is>
       </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -26223,6 +26363,11 @@
           <t>+0.816</t>
         </is>
       </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -27348,6 +27493,16 @@
           <t>+10.179</t>
         </is>
       </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -28003,6 +28158,16 @@
           <t>+10.472</t>
         </is>
       </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -28617,6 +28782,11 @@
           <t>+1.199</t>
         </is>
       </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -30267,6 +30437,11 @@
           <t>46.950</t>
         </is>
       </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>63942</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -31087,6 +31262,11 @@
           <t>1:49.323</t>
         </is>
       </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -32327,6 +32507,16 @@
           <t>3:10.126</t>
         </is>
       </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -32542,6 +32732,16 @@
           <t>+3.919</t>
         </is>
       </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -33882,6 +34082,11 @@
           <t>+0.922</t>
         </is>
       </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -34222,6 +34427,11 @@
           <t>+0.029</t>
         </is>
       </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -34982,6 +35192,11 @@
           <t>+1.423</t>
         </is>
       </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>63942</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -35877,6 +36092,11 @@
           <t>+0.739</t>
         </is>
       </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -36012,6 +36232,11 @@
           <t>+4.370</t>
         </is>
       </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -36767,6 +36992,11 @@
           <t>+4.164</t>
         </is>
       </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -37907,6 +38137,16 @@
           <t>+1.321</t>
         </is>
       </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -38410,6 +38650,11 @@
           <t>+0.371</t>
         </is>
       </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -39475,6 +39720,11 @@
           <t>+0.525</t>
         </is>
       </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>63942</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -40329,6 +40579,11 @@
           <t>+1.845</t>
         </is>
       </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -40823,6 +41078,11 @@
           <t>+2.006</t>
         </is>
       </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -41389,6 +41649,11 @@
           <t>+2.252</t>
         </is>
       </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -42166,6 +42431,16 @@
           <t>3:19.680</t>
         </is>
       </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -43229,6 +43504,16 @@
           <t>+2.489</t>
         </is>
       </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -43671,6 +43956,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -44466,6 +44756,11 @@
           <t>+0.726</t>
         </is>
       </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -46541,6 +46836,11 @@
           <t>+17.351</t>
         </is>
       </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -46846,6 +47146,16 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T658" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="U658" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -47586,9 +47896,24 @@
           <t>+5.698</t>
         </is>
       </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
       <c r="T667" t="inlineStr">
         <is>
           <t>42146</t>
+        </is>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>42148</t>
         </is>
       </c>
     </row>
@@ -47821,9 +48146,24 @@
           <t>+1.006</t>
         </is>
       </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>72154</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>75584</t>
+        </is>
+      </c>
       <c r="T670" t="inlineStr">
         <is>
           <t>70511</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>68980</t>
         </is>
       </c>
     </row>
@@ -48391,6 +48731,21 @@
           <t>69409</t>
         </is>
       </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -49061,6 +49416,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S686" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -50510,6 +50870,11 @@
           <t>+2.066</t>
         </is>
       </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -50860,6 +51225,16 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T712" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -51350,9 +51725,24 @@
           <t>+2.838</t>
         </is>
       </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="S718" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
       <c r="T718" t="inlineStr">
         <is>
           <t>42146</t>
+        </is>
+      </c>
+      <c r="U718" t="inlineStr">
+        <is>
+          <t>42148</t>
         </is>
       </c>
     </row>
@@ -51585,9 +51975,24 @@
           <t>+0.121</t>
         </is>
       </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>72154</t>
+        </is>
+      </c>
+      <c r="S721" t="inlineStr">
+        <is>
+          <t>75584</t>
+        </is>
+      </c>
       <c r="T721" t="inlineStr">
         <is>
           <t>70511</t>
+        </is>
+      </c>
+      <c r="U721" t="inlineStr">
+        <is>
+          <t>68980</t>
         </is>
       </c>
     </row>
@@ -51910,6 +52315,21 @@
           <t>69409</t>
         </is>
       </c>
+      <c r="S725" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
+      <c r="T725" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="U725" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -52650,6 +53070,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S735" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -53690,6 +54115,11 @@
           <t>+4.117</t>
         </is>
       </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -53980,6 +54410,16 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T754" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="U754" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -54885,9 +55325,24 @@
           <t>+1.157</t>
         </is>
       </c>
+      <c r="R765" t="inlineStr">
+        <is>
+          <t>72154</t>
+        </is>
+      </c>
+      <c r="S765" t="inlineStr">
+        <is>
+          <t>75584</t>
+        </is>
+      </c>
       <c r="T765" t="inlineStr">
         <is>
           <t>70511</t>
+        </is>
+      </c>
+      <c r="U765" t="inlineStr">
+        <is>
+          <t>68980</t>
         </is>
       </c>
     </row>
@@ -54960,6 +55415,21 @@
           <t>69409</t>
         </is>
       </c>
+      <c r="S766" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="T766" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="U766" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -56513,6 +56983,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S786" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -56575,6 +57050,11 @@
           <t>4:02.915</t>
         </is>
       </c>
+      <c r="R787" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -57973,9 +58453,24 @@
           <t>+2.605</t>
         </is>
       </c>
+      <c r="R806" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="S806" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
       <c r="T806" t="inlineStr">
         <is>
           <t>42146</t>
+        </is>
+      </c>
+      <c r="U806" t="inlineStr">
+        <is>
+          <t>42148</t>
         </is>
       </c>
     </row>
@@ -58132,6 +58627,16 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T808" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="U808" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -58977,6 +59482,21 @@
           <t>69409</t>
         </is>
       </c>
+      <c r="S818" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="T818" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="U818" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -59044,9 +59564,24 @@
           <t>+2.291</t>
         </is>
       </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>72154</t>
+        </is>
+      </c>
+      <c r="S819" t="inlineStr">
+        <is>
+          <t>75584</t>
+        </is>
+      </c>
       <c r="T819" t="inlineStr">
         <is>
           <t>70511</t>
+        </is>
+      </c>
+      <c r="U819" t="inlineStr">
+        <is>
+          <t>68980</t>
         </is>
       </c>
     </row>
@@ -59317,7 +59852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D227"/>
+  <dimension ref="A1:D244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64314,6 +64849,380 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ANOSHKIN</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>PODOLSKAIA</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Maryna</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>LITVINCHUK</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Aleksandr</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SERGEEV</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Maxim</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SPESIVTSEV</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Svetlana</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CHERNIGOVSKAYA</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Evgenii</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>LUKANTSOV</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Olesia</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ROMASENKO</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>63942</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Alena</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>NAZDROVA</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Mikita</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>BORYKAU</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>72154</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Uladzislau</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>LITVINAU</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>75584</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Dzmitry</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>NATYNCHYK</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Anastasiia</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>DOLGOVA</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Jose Ramon</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>PELIER CORDOVA</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
